--- a/batchstudent/Result/anlpvhe187047/TC3/GradeDetail.xlsx
+++ b/batchstudent/Result/anlpvhe187047/TC3/GradeDetail.xlsx
@@ -158,10 +158,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -170,12 +170,6 @@
     <x:t>Server responding (SYN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
@@ -192,18 +186,6 @@
   </x:si>
   <x:si>
     <x:t>{"StudentId":"S123","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -230,7 +212,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -239,17 +221,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -272,7 +244,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -282,14 +254,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -299,14 +265,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -933,11 +891,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R13"/>
+  <x:dimension ref="A1:R8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1044,25 +1002,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>47</x:v>
@@ -1100,7 +1058,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1120,8 +1078,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R3" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1141,10 +1099,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1156,7 +1114,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1176,8 +1134,8 @@
       <x:c r="Q4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R4" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R4" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1197,13 +1155,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>44</x:v>
@@ -1212,7 +1170,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1232,8 +1190,8 @@
       <x:c r="Q5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R5" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R5" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1253,10 +1211,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1268,7 +1226,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1288,8 +1246,8 @@
       <x:c r="Q6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R6" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1309,13 +1267,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>45</x:v>
@@ -1324,7 +1282,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1344,8 +1302,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R7" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1365,10 +1323,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1380,7 +1338,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1400,288 +1358,8 @@
       <x:c r="Q8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:18">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q9" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="R9" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:18">
-      <x:c r="A10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="0">
-        <x:v>44836</x:v>
-      </x:c>
-      <x:c r="Q10" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R10" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:18">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>44836</x:v>
-      </x:c>
-      <x:c r="R11" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:18">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="0">
-        <x:v>48182</x:v>
-      </x:c>
-      <x:c r="Q12" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R12" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:18">
-      <x:c r="A13" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="M13" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P13" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q13" s="0">
-        <x:v>48182</x:v>
-      </x:c>
-      <x:c r="R13" s="4" t="s">
-        <x:v>61</x:v>
+      <x:c r="R8" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
